--- a/encuesta_anonimizada.xlsx
+++ b/encuesta_anonimizada.xlsx
@@ -1234,7 +1234,7 @@
         <v>15</v>
       </c>
       <c r="C20" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D20" t="s">
         <v>24</v>
